--- a/data/trans_dic/P04D$notiene-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,8</t>
+          <t>3,78; 6,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,81; 25,01</t>
+          <t>18,87; 25,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 16,73</t>
+          <t>10,57; 16,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,09</t>
+          <t>4,43; 7,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 23,59</t>
+          <t>18,1; 23,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 13,95</t>
+          <t>10,41; 13,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,5</t>
+          <t>4,55; 6,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,41; 23,33</t>
+          <t>19,23; 23,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,92; 14,16</t>
+          <t>10,87; 14,21</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,07</t>
+          <t>3,22; 5,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,08</t>
+          <t>13,85; 17,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,28</t>
+          <t>7,28; 12,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,3</t>
+          <t>3,29; 5,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 14,03</t>
+          <t>10,93; 14,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 22,45</t>
+          <t>9,08; 21,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,86</t>
+          <t>3,5; 4,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 15,02</t>
+          <t>12,78; 14,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 16,44</t>
+          <t>9,11; 15,93</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,59</t>
+          <t>1,35; 4,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,0</t>
+          <t>6,58; 11,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,69</t>
+          <t>6,59; 11,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,23</t>
+          <t>1,12; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 13,48</t>
+          <t>7,94; 13,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,09</t>
+          <t>8,49; 12,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,66</t>
+          <t>1,5; 3,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,49</t>
+          <t>8,08; 11,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,69</t>
+          <t>8,05; 11,5</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,96</t>
+          <t>3,45; 4,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 17,1</t>
+          <t>14,55; 17,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,91</t>
+          <t>8,14; 12,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,27</t>
+          <t>3,83; 5,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 15,77</t>
+          <t>13,36; 15,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 18,89</t>
+          <t>9,93; 18,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 4,84</t>
+          <t>3,86; 4,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,27; 16,07</t>
+          <t>14,31; 16,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 15,06</t>
+          <t>9,69; 14,28</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37925; 66155</t>
+          <t>36777; 66455</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>141918; 188644</t>
+          <t>142334; 189113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53586; 85841</t>
+          <t>54213; 86095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60048; 94800</t>
+          <t>59278; 94231</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>182182; 234599</t>
+          <t>180077; 233633</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78804; 105317</t>
+          <t>78619; 105045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>106861; 150187</t>
+          <t>105242; 147964</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>339471; 408032</t>
+          <t>336252; 404797</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>138435; 179563</t>
+          <t>137834; 180152</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62755; 99214</t>
+          <t>63163; 100173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>282042; 354716</t>
+          <t>287533; 354680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167520; 280858</t>
+          <t>166338; 283270</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57731; 92915</t>
+          <t>57759; 93195</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>218564; 278956</t>
+          <t>217305; 278738</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>200140; 501311</t>
+          <t>202820; 489713</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>128952; 180419</t>
+          <t>129786; 178446</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>520659; 610597</t>
+          <t>519531; 609436</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>415698; 743066</t>
+          <t>411866; 720097</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6040; 22101</t>
+          <t>6515; 23147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35566; 65622</t>
+          <t>35959; 65373</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42905; 75576</t>
+          <t>42592; 75876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5017; 19401</t>
+          <t>5144; 19864</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44319; 74036</t>
+          <t>43593; 71963</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56027; 86144</t>
+          <t>55878; 85534</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13547; 34434</t>
+          <t>14092; 35192</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86882; 125932</t>
+          <t>88562; 129585</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106061; 152597</t>
+          <t>105003; 150021</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120450; 169175</t>
+          <t>117707; 169531</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>487341; 577691</t>
+          <t>491340; 575975</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>279587; 410386</t>
+          <t>280640; 414377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135233; 187003</t>
+          <t>135971; 187489</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>468625; 557047</t>
+          <t>471900; 553808</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>361612; 688839</t>
+          <t>361899; 663606</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>269765; 337085</t>
+          <t>268874; 341986</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>986121; 1110421</t>
+          <t>988780; 1118834</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>701246; 1068259</t>
+          <t>687463; 1012501</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$notiene-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,83</t>
+          <t>3,98; 6,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 25,07</t>
+          <t>19,06; 24,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 16,78</t>
+          <t>11,61; 17,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,04</t>
+          <t>4,5; 7,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,1; 23,49</t>
+          <t>18,3; 23,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 13,92</t>
+          <t>11,12; 14,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,4</t>
+          <t>4,62; 6,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,23; 23,14</t>
+          <t>19,16; 23,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 14,21</t>
+          <t>11,78; 15,16</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,11</t>
+          <t>3,29; 5,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,85; 17,08</t>
+          <t>13,82; 17,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 12,39</t>
+          <t>10,65; 14,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,31</t>
+          <t>3,32; 5,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,93; 14,02</t>
+          <t>11,16; 14,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 21,93</t>
+          <t>11,24; 13,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,81</t>
+          <t>3,5; 4,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 14,99</t>
+          <t>12,85; 15,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 15,93</t>
+          <t>11,28; 13,53</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,81</t>
+          <t>1,25; 4,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 11,95</t>
+          <t>6,68; 12,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 11,73</t>
+          <t>8,2; 13,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,33</t>
+          <t>1,11; 4,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 13,1</t>
+          <t>8,06; 13,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,99</t>
+          <t>9,24; 13,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,74</t>
+          <t>1,48; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 11,82</t>
+          <t>7,98; 11,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,5</t>
+          <t>9,44; 12,62</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 4,97</t>
+          <t>3,52; 5,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 17,05</t>
+          <t>14,54; 17,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 12,03</t>
+          <t>11,18; 13,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,28</t>
+          <t>3,87; 5,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,36; 15,68</t>
+          <t>13,3; 15,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 18,2</t>
+          <t>11,25; 13,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 4,91</t>
+          <t>3,83; 4,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 16,19</t>
+          <t>14,25; 15,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,28</t>
+          <t>11,53; 13,08</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68152</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91061</t>
+          <t>105389</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>159213</t>
+          <t>187704</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36777; 66455</t>
+          <t>38732; 65098</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>142334; 189113</t>
+          <t>143771; 188121</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54213; 86095</t>
+          <t>66926; 100853</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59278; 94231</t>
+          <t>60223; 93693</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>180077; 233633</t>
+          <t>182056; 232295</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78619; 105045</t>
+          <t>91342; 122942</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>105242; 147964</t>
+          <t>106690; 150382</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>336252; 404797</t>
+          <t>335139; 407277</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>137834; 180152</t>
+          <t>164624; 211926</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>233623</t>
+          <t>272865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>282914</t>
+          <t>268239</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>516537</t>
+          <t>541103</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63163; 100173</t>
+          <t>64420; 99072</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>287533; 354680</t>
+          <t>287056; 355565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166338; 283270</t>
+          <t>236681; 313187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57759; 93195</t>
+          <t>58202; 93798</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>217305; 278738</t>
+          <t>221840; 281012</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>202820; 489713</t>
+          <t>243517; 299908</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>129786; 178446</t>
+          <t>130079; 178032</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>519531; 609436</t>
+          <t>522272; 611748</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>411866; 720097</t>
+          <t>494998; 593745</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57579</t>
+          <t>76114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69265</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>126844</t>
+          <t>157948</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6515; 23147</t>
+          <t>5996; 21163</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35959; 65373</t>
+          <t>36533; 66454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42592; 75876</t>
+          <t>58355; 99032</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5144; 19864</t>
+          <t>5086; 19758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43593; 71963</t>
+          <t>44243; 73597</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55878; 85534</t>
+          <t>67589; 98383</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14092; 35192</t>
+          <t>13934; 34001</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>88562; 129585</t>
+          <t>87514; 126872</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>105003; 150021</t>
+          <t>136255; 182087</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359354</t>
+          <t>431293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>443240</t>
+          <t>455462</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>802593</t>
+          <t>886755</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>117707; 169531</t>
+          <t>120021; 171233</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>491340; 575975</t>
+          <t>491109; 578094</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>280640; 414377</t>
+          <t>392645; 482274</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135971; 187489</t>
+          <t>137399; 187394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>471900; 553808</t>
+          <t>469694; 553359</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>361899; 663606</t>
+          <t>418452; 491589</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>268874; 341986</t>
+          <t>266599; 338334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>988780; 1118834</t>
+          <t>984658; 1104253</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>687463; 1012501</t>
+          <t>833596; 945755</t>
         </is>
       </c>
     </row>
